--- a/product_upload/packages/24/file.xlsx
+++ b/product_upload/packages/24/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>ELICA 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-3490E7430A8A</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1046,6 +1056,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>EMIDOL 120MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-1E0221839320</t>
         </is>
       </c>
@@ -1069,7 +1084,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1244,6 +1259,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>EMIDOL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-8ADFBF3428DD</t>
         </is>
       </c>
@@ -1267,7 +1287,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1438,6 +1458,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>ENAPRIL 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-99BA1D7590F9</t>
         </is>
       </c>
@@ -1461,7 +1486,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1632,6 +1657,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>ENABLEX 7.5MG PROLONGED RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-6FD9FC72CA8D</t>
         </is>
       </c>
@@ -1655,7 +1685,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1830,6 +1860,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>ENABLEX 15MG PROLONGED RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-2C3F2113A0B9</t>
         </is>
       </c>
@@ -1853,7 +1888,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2024,6 +2059,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>E-MOX 250MG DRY MIX.</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-3D575F2D8575</t>
         </is>
       </c>
@@ -2047,7 +2087,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2210,6 +2250,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>E-MOX 125MG DRY MIX.</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-5E7A81803BDB</t>
         </is>
       </c>
@@ -2233,7 +2278,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2396,6 +2441,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>EMIMYCIN 500 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-2F608E07D61A</t>
         </is>
       </c>
@@ -2419,7 +2469,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2598,6 +2648,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>EMILOK 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-D72034E7F40F</t>
         </is>
       </c>
@@ -2621,7 +2676,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2796,6 +2851,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>EMIFENAC 50 MG DISPERSABLE TAB.</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-69C7C39EFDCB</t>
         </is>
       </c>
@@ -2819,7 +2879,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2998,6 +3058,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>EMIFEN 600 MG F-C TAB</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-B98FC41813D5</t>
         </is>
       </c>
@@ -3021,7 +3086,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3196,6 +3261,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>EMIFEN 100MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-8BE41C0CA3A9</t>
         </is>
       </c>
@@ -3219,7 +3289,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3386,6 +3456,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>E-MOX 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-44E132F0F806</t>
         </is>
       </c>
@@ -3409,7 +3484,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3580,6 +3655,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>EXJADE 250MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-CDC06C6B1C4D</t>
         </is>
       </c>
@@ -3603,7 +3683,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3774,6 +3854,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>EXJADE 125MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-2CDAF8F07DBD</t>
         </is>
       </c>
@@ -3797,7 +3882,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3968,6 +4053,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>EXFORGE HCT 5MG/160MG/25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-F7D01B665645</t>
         </is>
       </c>
@@ -3991,7 +4081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4162,6 +4252,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>EXFORGE HCT 5MG/160MG/12.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-A36854BEC4B6</t>
         </is>
       </c>
@@ -4185,7 +4280,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4360,6 +4455,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>EXFORGE HCT 10MG/320MG/25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-93EF2C703805</t>
         </is>
       </c>
@@ -4383,7 +4483,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4550,6 +4650,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>EXFORGE HCT 10MG/160MG/25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-2AB15AE08299</t>
         </is>
       </c>
@@ -4573,7 +4678,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4744,6 +4849,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>EXFORGE HCT 10MG/160MG/12.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-AE38B124FA44</t>
         </is>
       </c>
@@ -4767,7 +4877,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4938,6 +5048,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>EXFORGE 5MG-160 MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-5E0AC17B9572</t>
         </is>
       </c>
@@ -4961,7 +5076,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5132,6 +5247,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>EXFORGE 10 MG-160 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-773B543A6F67</t>
         </is>
       </c>
@@ -5155,7 +5275,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5326,6 +5446,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>EXELON 9.5MG-24H TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-CEA04D6B975F</t>
         </is>
       </c>
@@ -5349,7 +5474,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5516,6 +5641,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>EXELON 6 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-1383E19C2B36</t>
         </is>
       </c>
@@ -5539,7 +5669,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5710,6 +5840,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>EXELON 4.6MG-24H TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-4D85607C16F3</t>
         </is>
       </c>
@@ -5733,7 +5868,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5900,6 +6035,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>EXELON 3 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-BB412C73719F</t>
         </is>
       </c>
@@ -5923,7 +6063,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6090,6 +6230,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>EXELON 1.5 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-473CFAC76EE6</t>
         </is>
       </c>
@@ -6113,7 +6258,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6284,6 +6429,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>EXJADE 500MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-DFDE4966EEF3</t>
         </is>
       </c>
@@ -6307,7 +6457,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6478,6 +6628,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>EXYLIN PEDIATRIC SYRUP</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-961A12B26041</t>
         </is>
       </c>
@@ -6501,7 +6656,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6668,6 +6823,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>EXYLIN SYRUP 14MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-973932BF5501</t>
         </is>
       </c>
@@ -6691,7 +6851,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6862,6 +7022,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>FASTUM 2.5% GEL</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-CAD1C197A9FD</t>
         </is>
       </c>
@@ -6885,7 +7050,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -7056,6 +7221,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>FAST- FLAM 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-C0DBCDD9F6E5</t>
         </is>
       </c>
@@ -7079,7 +7249,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7246,6 +7416,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>FARCOLIN 0.5% RESPIRATOR Solution</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-FB7BFB5D8200</t>
         </is>
       </c>
@@ -7269,7 +7444,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7428,6 +7603,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>FAMPYRA 10MG Prolonged-release tablet</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-5ADF8B3E6FB2</t>
         </is>
       </c>
@@ -7451,7 +7631,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7614,6 +7794,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>FALLAH 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-5474870D8951</t>
         </is>
       </c>
@@ -7637,7 +7822,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7810,6 +7995,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>EVRA TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-4421D3F88721</t>
         </is>
       </c>
@@ -7833,7 +8023,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7988,6 +8178,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>FALLAH 25 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-9D850E27160F</t>
         </is>
       </c>
@@ -8011,7 +8206,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8170,6 +8365,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>FACTIVE 320MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-9C503E971AD3</t>
         </is>
       </c>
@@ -8193,7 +8393,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8352,6 +8552,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>FACTIVE 320MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-391EF249FA8D</t>
         </is>
       </c>
@@ -8375,7 +8580,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8550,6 +8755,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>EZOLVIN 8MGTAB</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-74E050056853</t>
         </is>
       </c>
@@ -8573,7 +8783,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8748,6 +8958,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>EZOLVIN 4MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-6D4AFB1B1897</t>
         </is>
       </c>
@@ -8771,7 +8986,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8938,6 +9153,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>EZIPECT 12.5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-B2B8C619E609</t>
         </is>
       </c>
@@ -8961,7 +9181,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9128,6 +9348,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>EZILAX 10G-15ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-372852D62DE2</t>
         </is>
       </c>
@@ -9151,7 +9376,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9314,6 +9539,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>EYLOX 0.3% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-2E51C0662952</t>
         </is>
       </c>
@@ -9337,7 +9567,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9496,6 +9726,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>FALLAH 100 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-8AD82526361B</t>
         </is>
       </c>
@@ -9519,7 +9754,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9682,6 +9917,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>EVIT 400MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-D91F2E4968D6</t>
         </is>
       </c>
@@ -9705,7 +9945,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9872,6 +10112,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>ERECTA 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-13AA30DCB3E4</t>
         </is>
       </c>
@@ -9895,7 +10140,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10054,6 +10299,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ERACID 500MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-2E29532F8E27</t>
         </is>
       </c>
@@ -10077,7 +10327,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10244,6 +10494,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>ERACID 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-7369A1DCA19A</t>
         </is>
       </c>
@@ -10267,7 +10522,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10438,6 +10693,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ERECTA 100 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-85E80887E7F6</t>
         </is>
       </c>
@@ -10461,7 +10721,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10620,6 +10880,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ELDOQUIN FORT 4% CREAM</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-9849E1E1D6E5</t>
         </is>
       </c>
@@ -10643,7 +10908,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10822,6 +11087,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>EUTHYROX</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-540E27217441</t>
         </is>
       </c>
@@ -10845,7 +11115,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -11020,6 +11290,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>EUTHYROX</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-29CC7A8684ED</t>
         </is>
       </c>
@@ -11043,7 +11318,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11218,6 +11493,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>EUTHYROX</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-30CEDE3B8D0C</t>
         </is>
       </c>
@@ -11241,7 +11521,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11412,6 +11692,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>EUTHYROX</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-DA20D96A7F4E</t>
         </is>
       </c>
@@ -11435,7 +11720,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11598,6 +11883,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>EUDYNA GEL 0.05%</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-85A0CBDD4D49</t>
         </is>
       </c>
@@ -11621,7 +11911,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11790,6 +12080,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>EUCARBON TAB</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-22F259F89668</t>
         </is>
       </c>
@@ -11813,7 +12108,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11974,6 +12269,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>EUCARBON</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-C558C7FA42E7</t>
         </is>
       </c>
@@ -11997,7 +12297,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12172,6 +12472,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>ETRIVEX 0.05% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-3C473F1CB95C</t>
         </is>
       </c>
@@ -12195,7 +12500,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12368,6 +12673,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>ETORIA 90MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-428028252033</t>
         </is>
       </c>
@@ -12391,7 +12701,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12564,6 +12874,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>ETORIA 60MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-6DBEADB9EEFC</t>
         </is>
       </c>
@@ -12587,7 +12902,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12756,6 +13071,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>ETORIA 120MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-8146EFB90405</t>
         </is>
       </c>
@@ -12779,7 +13099,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12938,6 +13258,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>EUDYNA CREAM 0.05%</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-5062ECFEEEFF</t>
         </is>
       </c>
@@ -12961,7 +13286,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13124,6 +13449,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-C2547F25E35F</t>
         </is>
       </c>
@@ -13147,7 +13477,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13306,6 +13636,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>L-CET 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-656C5FE63CCD</t>
         </is>
       </c>
@@ -13329,7 +13664,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13494,6 +13829,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>STABLIX 0.5 ML SUSPENSION FOR INJECTION Vials</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-02320334F5A6</t>
         </is>
       </c>
@@ -13517,7 +13857,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13676,6 +14016,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>VITREAL S OPHTHALMIC SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-C6EEA72470DF</t>
         </is>
       </c>
@@ -13699,7 +14044,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13858,6 +14203,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>ROFLAST 500 mcg</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-DF66ADEEC430</t>
         </is>
       </c>
@@ -13881,7 +14231,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14048,6 +14398,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>HUMALOG KWIK-PEN MIX 25</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-DA02E946F69A</t>
         </is>
       </c>
@@ -14071,7 +14426,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14238,6 +14593,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>HUMALOG KWIK-PEN 100IU/ML</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-357BA07914A2</t>
         </is>
       </c>
@@ -14261,7 +14621,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14432,6 +14792,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>OTEZLA 30MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-E507B5F2E49C</t>
         </is>
       </c>
@@ -14455,7 +14820,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14618,6 +14983,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ACCEPT 500MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-9BC51BBB1300</t>
         </is>
       </c>
@@ -14641,7 +15011,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14804,6 +15174,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t xml:space="preserve">ALLERCET 5MG F.C.TABLET                     </t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-331B8EC8C4BF</t>
         </is>
       </c>
@@ -14827,7 +15202,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14990,6 +15365,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t xml:space="preserve">ALLERCET 5MG F.C.TABLET                     </t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-BDA59EFA1907</t>
         </is>
       </c>
@@ -15013,7 +15393,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15184,6 +15564,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Relaxon Forte 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-247F8A3585A5</t>
         </is>
       </c>
@@ -15207,7 +15592,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15374,6 +15759,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>OTEZLA 10 mg 4 tablets + 20 mg 4 tablets + 30 mg 19 tablets</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-FAAB5D71BDB6</t>
         </is>
       </c>
@@ -15397,7 +15787,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15560,6 +15950,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>DETREMIN 20000IU/ML ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-B4552AF2ED60</t>
         </is>
       </c>
@@ -15583,7 +15978,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15746,6 +16141,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>ARXIA 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-1FBC183D5615</t>
         </is>
       </c>
@@ -15769,7 +16169,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15928,6 +16328,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>ARXIA 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-93788B0F8506</t>
         </is>
       </c>
@@ -15951,7 +16356,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16114,6 +16519,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ROXARDIO 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-C61794C985CD</t>
         </is>
       </c>
@@ -16137,7 +16547,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16300,6 +16710,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>ROXARDIO 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-D623A9757142</t>
         </is>
       </c>
@@ -16323,7 +16738,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16478,6 +16893,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>COVATEL</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-6A4AE54E3D76</t>
         </is>
       </c>
@@ -16501,7 +16921,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16660,6 +17080,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>COVATEL</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-A0EB39C61334</t>
         </is>
       </c>
@@ -16683,7 +17108,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16850,6 +17275,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>VERCANZA 450 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-F57F95561AA0</t>
         </is>
       </c>
@@ -16873,7 +17303,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -17044,6 +17474,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>LEUKAIR 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-7EF1257222C3</t>
         </is>
       </c>
@@ -17067,7 +17502,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17230,6 +17665,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>FOSTER NEXTHALER 100MCG/6MCG INHALATION POWDER</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-81F597AFE4FC</t>
         </is>
       </c>
@@ -17253,7 +17693,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17416,6 +17856,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>LETIREM 1000 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-6EA20ED634A8</t>
         </is>
       </c>
@@ -17439,7 +17884,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17598,6 +18043,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>LETIREM 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-5A207AFF8538</t>
         </is>
       </c>
@@ -17621,7 +18071,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17780,6 +18230,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>LETIREM 250 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-511456F99BA8</t>
         </is>
       </c>
@@ -17803,7 +18258,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17982,6 +18437,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Fostimon 300 I.U</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-DE6AFC73B576</t>
         </is>
       </c>
@@ -18005,7 +18465,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18184,6 +18644,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Fostimon 225 I.U</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-EFF60198F533</t>
         </is>
       </c>
@@ -18207,7 +18672,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18366,6 +18831,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>SARFEX 180MG F.C.TAB.(30S)</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-3942A31270B4</t>
         </is>
       </c>
@@ -18389,7 +18859,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18552,6 +19022,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>SARFEX 180MG F.C.TAB.(10S)</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-468CFDD8F349</t>
         </is>
       </c>
@@ -18575,7 +19050,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18742,6 +19217,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Artelac Night Time Gel</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-BDFDB0D0A5C8</t>
         </is>
       </c>
@@ -18765,7 +19245,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18932,6 +19412,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>VELTASSA 16.8G SACHET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-E7921C30F98D</t>
         </is>
       </c>
@@ -18955,7 +19440,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19118,6 +19603,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>VELTASSA 8.4G SACHET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-FC18A0C8D365</t>
         </is>
       </c>
@@ -19141,7 +19631,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19308,6 +19798,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>MEBAGEN SR 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-2FEFB7CBD087</t>
         </is>
       </c>
@@ -19331,7 +19826,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19498,6 +19993,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>AERIALLERG 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-DB2FEAD0EBDB</t>
         </is>
       </c>
@@ -19521,7 +20021,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19685,6 +20185,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>SENERGY 10 MG/160 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-B05453FDCFE8</t>
         </is>
@@ -19701,7 +20206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19747,100 +20252,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19872,7 +20382,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19887,92 +20397,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-53576</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>395.23</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>164</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20004,7 +20519,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20019,92 +20534,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-76595</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>195.22</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>165</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20136,7 +20656,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20151,92 +20671,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-98410</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>150.12</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>166</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20268,7 +20793,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20283,92 +20808,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-34503</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>203.74</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>167</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20400,7 +20930,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20415,92 +20945,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-39453</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>165.12</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>168</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20532,7 +21067,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20547,92 +21082,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-53718</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>289.25</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>169</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20664,7 +21204,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20679,92 +21219,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-16779</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>355.79</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>170</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20796,7 +21341,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20811,92 +21356,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-23858</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>287.73</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>171</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20928,7 +21478,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20943,92 +21493,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-20938</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>230.33</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>172</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21060,7 +21615,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21075,92 +21630,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-38980</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>252.08</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>173</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21192,7 +21752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21207,92 +21767,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-69072</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>329.77</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>174</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21309,7 +21874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21415,6 +21980,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21450,7 +22025,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21515,6 +22090,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-DB5CEBEF625E</t>
         </is>
@@ -21551,7 +22136,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21616,6 +22201,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-D33ABEC1871A</t>
         </is>
@@ -21652,7 +22247,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21717,6 +22312,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-CDCE28CB7E70</t>
         </is>
@@ -21753,7 +22358,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21818,6 +22423,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-983FA215DFA9</t>
         </is>
@@ -21854,7 +22469,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21919,6 +22534,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-F3804820E896</t>
         </is>
@@ -21955,7 +22580,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22020,6 +22645,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-B0AC1CCE2227</t>
         </is>
@@ -22056,7 +22691,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22121,6 +22756,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-5C80775275CE</t>
         </is>
@@ -22157,7 +22802,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22222,6 +22867,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-2B45D7815E60</t>
         </is>
@@ -22258,7 +22913,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22323,6 +22978,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-EE6087E76970</t>
         </is>
@@ -22359,7 +23024,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22424,6 +23089,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-8F9A9B7DEF13</t>
         </is>
@@ -22460,7 +23135,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22525,6 +23200,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-24EC34E9082A</t>
         </is>
@@ -22561,7 +23246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22626,6 +23311,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-73058BA0D6DE</t>
         </is>
@@ -22662,7 +23357,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22727,6 +23422,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-29DF5C58F7F5</t>
         </is>
@@ -22763,7 +23468,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22828,6 +23533,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-92E88F8E3C70</t>
         </is>
@@ -22864,7 +23579,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22929,6 +23644,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-BB82870EB1E5</t>
         </is>
@@ -22965,7 +23690,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23030,6 +23755,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-88FCF1F96BA6</t>
         </is>
@@ -23066,7 +23801,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23131,6 +23866,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-B0DE2601CBB2</t>
         </is>
@@ -23167,7 +23912,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23232,6 +23977,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-AC23FD0D11F3</t>
         </is>
@@ -23268,7 +24023,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23333,6 +24088,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-379183B2EACA</t>
         </is>
@@ -23369,7 +24134,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23434,6 +24199,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-1069B230B143</t>
         </is>

--- a/product_upload/packages/24/file.xlsx
+++ b/product_upload/packages/24/file.xlsx
@@ -2095,8 +2095,16 @@
           <t>9209341920-395-705127037815</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ E-MOX 125MG DRY MIX.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>E-MOX 125MG DRY MIX. detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2286,8 +2294,16 @@
           <t>3251953734-771-236025200406</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMIMYCIN 500 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>EMIMYCIN 500 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -7452,8 +7468,16 @@
           <t>9909964753-873-754118900141</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FAMPYRA 10MG Prolonged-release tablet</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>FAMPYRA 10MG Prolonged-release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7639,8 +7663,16 @@
           <t>1733415954-475-851191889468</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FALLAH 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>FALLAH 50 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -8031,8 +8063,16 @@
           <t>0624604143-505-525231368575</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FALLAH 25 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>FALLAH 25 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8214,8 +8254,16 @@
           <t>4109449798-361-414992351779</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FACTIVE 320MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>FACTIVE 320MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8401,8 +8449,16 @@
           <t>3831631518-750-363922190441</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FACTIVE 320MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>FACTIVE 320MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -9575,8 +9631,16 @@
           <t>6946129545-650-117135905302</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FALLAH 100 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>FALLAH 100 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -10148,8 +10212,16 @@
           <t>1536428625-829-069794528197</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ERACID 500MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ERACID 500MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10729,8 +10801,16 @@
           <t>3240517906-733-362276301974</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELDOQUIN FORT 4% CREAM</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ELDOQUIN FORT 4% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -11728,8 +11808,16 @@
           <t>8627726603-959-358285127424</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EUDYNA GEL 0.05%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>EUDYNA GEL 0.05% detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -12116,8 +12204,16 @@
           <t>5814721618-503-890344178854</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EUCARBON</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>EUCARBON detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -13107,8 +13203,16 @@
           <t>1846656729-588-437101367064</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EUDYNA CREAM 0.05%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>EUDYNA CREAM 0.05% detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13294,8 +13398,16 @@
           <t>5008004338-627-360234662853</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CO-VALISTA detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13485,8 +13597,16 @@
           <t>1093636442-787-984016312244</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ L-CET 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L-CET 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13672,8 +13792,16 @@
           <t>1389958877-804-874691478445</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STABLIX 0.5 ML SUSPENSION FOR INJECTION Vials</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>STABLIX 0.5 ML SUSPENSION FOR INJECTION Vials detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>ARAB COMPANY FOR PHARMACEUTICAL PRODUCTS (ARABIO)</t>
@@ -13865,8 +13993,16 @@
           <t>9024226687-889-385629306690</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VITREAL S OPHTHALMIC SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>VITREAL S OPHTHALMIC SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -14052,8 +14188,16 @@
           <t>3005530874-958-059353774768</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROFLAST 500 mcg</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ROFLAST 500 mcg detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14828,8 +14972,16 @@
           <t>3321106607-797-279468363577</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACCEPT 500MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACCEPT 500MG F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -15019,8 +15171,16 @@
           <t>5705438967-408-835100598798</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERCET 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ALLERCET 5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15210,8 +15370,16 @@
           <t>3843163423-197-286931930007</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERCET 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ALLERCET 5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15986,8 +16154,16 @@
           <t>9026987639-172-728879497290</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARXIA 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ARXIA 60MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16177,8 +16353,16 @@
           <t>5734078093-162-375746559678</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARXIA 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ARXIA 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16364,8 +16548,16 @@
           <t>0604983970-960-540751320839</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROXARDIO 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ROXARDIO 20MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16555,8 +16747,16 @@
           <t>6167147965-095-480407102922</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROXARDIO 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ROXARDIO 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16746,8 +16946,16 @@
           <t>1956689119-462-839916160600</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVATEL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>COVATEL detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16929,8 +17137,16 @@
           <t>3141491156-541-586910869100</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVATEL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>COVATEL detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17701,8 +17917,16 @@
           <t>8012177779-886-063771028445</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LETIREM 1000 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>LETIREM 1000 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17892,8 +18116,16 @@
           <t>8873391710-969-838369796389</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LETIREM 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>LETIREM 500 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -18079,8 +18311,16 @@
           <t>2563332542-920-211314075975</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LETIREM 250 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>LETIREM 250 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18680,8 +18920,16 @@
           <t>8849950525-688-288410764595</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SARFEX 180MG F.C.TAB.(30S)</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>SARFEX 180MG F.C.TAB.(30S) detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18867,8 +19115,16 @@
           <t>7287767463-240-682774365961</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SARFEX 180MG F.C.TAB.(10S)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>SARFEX 180MG F.C.TAB.(10S) detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19834,8 +20090,16 @@
           <t>8478623639-764-954335363124</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AERIALLERG 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>AERIALLERG 5MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/24/file.xlsx
+++ b/product_upload/packages/24/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22138,7 +22138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22219,40 +22219,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22332,38 +22337,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>428.52</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-DB5CEBEF625E</t>
         </is>
@@ -22443,38 +22453,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>457.59</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-D33ABEC1871A</t>
         </is>
@@ -22554,38 +22569,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>472.96</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-CDCE28CB7E70</t>
         </is>
@@ -22665,38 +22685,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>89.41</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-983FA215DFA9</t>
         </is>
@@ -22776,38 +22801,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>216.23</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-F3804820E896</t>
         </is>
@@ -22887,38 +22917,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>490.32</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-B0AC1CCE2227</t>
         </is>
@@ -22998,38 +23033,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>218.01</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-5C80775275CE</t>
         </is>
@@ -23109,38 +23149,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>34.24</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-2B45D7815E60</t>
         </is>
@@ -23220,38 +23265,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>466.04</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-EE6087E76970</t>
         </is>
@@ -23331,38 +23381,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>51.29</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-8F9A9B7DEF13</t>
         </is>
@@ -23442,38 +23497,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>260.57</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-24EC34E9082A</t>
         </is>
@@ -23553,38 +23613,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>182.57</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-73058BA0D6DE</t>
         </is>
@@ -23664,38 +23729,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>88.14</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-29DF5C58F7F5</t>
         </is>
@@ -23775,38 +23845,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>350.38</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-92E88F8E3C70</t>
         </is>
@@ -23886,38 +23961,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>465.29</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-BB82870EB1E5</t>
         </is>
@@ -23997,38 +24077,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>319.73</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-88FCF1F96BA6</t>
         </is>
@@ -24108,38 +24193,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>211.87</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-B0DE2601CBB2</t>
         </is>
@@ -24219,38 +24309,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>294.33</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-AC23FD0D11F3</t>
         </is>
@@ -24330,38 +24425,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>376.15</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-379183B2EACA</t>
         </is>
@@ -24441,38 +24541,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>200.77</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-1069B230B143</t>
         </is>
